--- a/business_forms/023_performance_metrics_audit_form--business_forms.xlsx
+++ b/business_forms/023_performance_metrics_audit_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>company_performance_metrics</t>
+          <t>Company Performance Metrics</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>team_performance_metrics</t>
+          <t>team_performance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>team_performance_metrics</t>
+          <t>Team Performance</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>employee_performance_metrics</t>
+          <t>employee_performance</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>employee_performance_metrics</t>
+          <t>Employee Performance</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,40 +584,40 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>customer_performance_metrics</t>
+          <t>customer_satisfaction</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>customer_performance_metrics</t>
+          <t>Customer Satisfaction</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>customer_satisfaction_metrics</t>
+          <t>process_performance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>customer_satisfaction_metrics</t>
+          <t>Process Performance</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>customer_satisfaction_metrics</t>
+          <t>business_process</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>customer_satisfaction_metrics</t>
+          <t>Business Process</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,41 +658,41 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>customer_satisfaction_metrics</t>
+          <t>product_quality</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>customer_satisfaction_metrics</t>
+          <t>Product Quality</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>product_performance_metrics</t>
+          <t>customer_satisfaction_comments</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>product_performance_metrics</t>
+          <t>Customer Satisfaction Comments</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>product_performance_metrics</t>
+          <t>company_performance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>product_performance_metrics</t>
+          <t>Company Performance</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,18 +727,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>process_performance_metrics</t>
+          <t>business_process_metrics</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>process_performance_metrics</t>
+          <t>Business Process Metrics</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>process_performance_metrics</t>
+          <t>product_quality_metrics</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>process_performance_metrics</t>
+          <t>Product Quality Metrics</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>business_performance_metrics</t>
+          <t>process_metrics</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>business_performance_metrics</t>
+          <t>Process Metrics</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,18 +796,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>business_performance_metrics</t>
+          <t>company_satisfaction</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>business_performance_metrics</t>
+          <t>Company Satisfaction</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,108 +819,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>business_performance_metrics</t>
+          <t>business_process_satisfaction</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>business_performance_metrics</t>
+          <t>Business Process Satisfaction</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>company_performance_metrics</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>company_performance_metrics</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>company_performance_metrics</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>company_performance_metrics</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>business_process_metrics</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>business_process_metrics</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>customer_satisfaction</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>customer_satisfaction</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -937,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -970,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -987,556 +895,624 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>team_performance_metrics_choices</t>
+          <t>company_performance_metrics_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>team_performance_metrics_choices</t>
+          <t>team_performance_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>employee_performance_metrics_choices</t>
+          <t>team_performance_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>employee_performance_metrics_choices</t>
+          <t>team_performance_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>customer_performance_metrics_choices</t>
+          <t>employee_performance_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>customer_performance_metrics_choices</t>
+          <t>employee_performance_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>customer_satisfaction_metrics_choices</t>
+          <t>employee_performance_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>customer_satisfaction_metrics_choices</t>
+          <t>customer_satisfaction_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>dissatisfied</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dissatisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>customer_satisfaction_metrics_choices</t>
+          <t>customer_satisfaction_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>customer_satisfaction_metrics_choices</t>
+          <t>process_performance_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>dissatisfied</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dissatisfied</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>customer_satisfaction_metrics_choices</t>
+          <t>process_performance_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>customer_satisfaction_metrics_choices</t>
+          <t>process_performance_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>dissatisfied</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dissatisfied</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>product_performance_metrics_choices</t>
+          <t>business_process_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>product_performance_metrics_choices</t>
+          <t>business_process_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>product_performance_metrics_choices</t>
+          <t>business_process_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>product_performance_metrics_choices</t>
+          <t>product_quality_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>process_performance_metrics_choices</t>
+          <t>product_quality_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>process_performance_metrics_choices</t>
+          <t>product_quality_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>process_performance_metrics_choices</t>
+          <t>company_performance_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>process_performance_metrics_choices</t>
+          <t>company_performance_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>business_performance_metrics_choices</t>
+          <t>company_performance_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>business_performance_metrics_choices</t>
+          <t>business_process_metrics_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>business_performance_metrics_choices</t>
+          <t>business_process_metrics_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>business_performance_metrics_choices</t>
+          <t>business_process_metrics_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>business_performance_metrics_choices</t>
+          <t>product_quality_metrics_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>business_performance_metrics_choices</t>
+          <t>product_quality_metrics_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>company_performance_metrics_choices</t>
+          <t>product_quality_metrics_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>company_performance_metrics_choices</t>
+          <t>process_metrics_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>company_performance_metrics_choices</t>
+          <t>process_metrics_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>company_performance_metrics_choices</t>
+          <t>process_metrics_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>business_process_metrics_choices</t>
+          <t>company_satisfaction_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>business_process_metrics_choices</t>
+          <t>company_satisfaction_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>company_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>business_process_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>business_process_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>business_process_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Poor</t>
         </is>
       </c>
     </row>
